--- a/output/daily_ratings/uk_ratings_2026-05-28.xlsx
+++ b/output/daily_ratings/uk_ratings_2026-05-28.xlsx
@@ -522,18 +522,18 @@
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Citrus Springs (USA)</t>
+          <t>High King (IRE)</t>
         </is>
       </c>
       <c r="I2" t="n">
         <v>2</v>
       </c>
       <c r="J2" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -542,14 +542,16 @@
       <c r="M2" t="n">
         <v>77.34</v>
       </c>
-      <c r="N2" t="inlineStr"/>
+      <c r="N2" t="n">
+        <v>78.7</v>
+      </c>
       <c r="O2" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>-9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -576,28 +578,30 @@
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>High King (IRE)</t>
+          <t>Joga Bonito</t>
         </is>
       </c>
       <c r="I3" t="n">
         <v>2</v>
       </c>
       <c r="J3" t="n">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
-      <c r="L3" t="inlineStr"/>
+      <c r="L3" t="n">
+        <v>3.5</v>
+      </c>
       <c r="M3" t="n">
         <v>77.34</v>
       </c>
       <c r="N3" t="n">
-        <v>78.7</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -632,30 +636,30 @@
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Joga Bonito</t>
+          <t>Lars Soldier (IRE)</t>
         </is>
       </c>
       <c r="I4" t="n">
         <v>2</v>
       </c>
       <c r="J4" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="M4" t="n">
         <v>77.34</v>
       </c>
       <c r="N4" t="n">
-        <v>66.09999999999999</v>
+        <v>63.1</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -690,30 +694,30 @@
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Lars Soldier (IRE)</t>
+          <t>Pisiffik Ginger (IRE)</t>
         </is>
       </c>
       <c r="I5" t="n">
         <v>2</v>
       </c>
       <c r="J5" t="n">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="M5" t="n">
         <v>77.34</v>
       </c>
       <c r="N5" t="n">
-        <v>65.5</v>
+        <v>56.5</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -721,7 +725,7 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="6">
@@ -748,30 +752,30 @@
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Pisiffik Ginger (IRE)</t>
+          <t>I Ready (IRE)</t>
         </is>
       </c>
       <c r="I6" t="n">
         <v>2</v>
       </c>
       <c r="J6" t="n">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="M6" t="n">
         <v>77.34</v>
       </c>
       <c r="N6" t="n">
-        <v>56.5</v>
+        <v>57.8</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -779,7 +783,7 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -806,30 +810,30 @@
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>I Ready (IRE)</t>
+          <t>Magical Moonlight (IRE)</t>
         </is>
       </c>
       <c r="I7" t="n">
         <v>2</v>
       </c>
       <c r="J7" t="n">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>5.6</v>
+        <v>8.6</v>
       </c>
       <c r="M7" t="n">
         <v>77.34</v>
       </c>
       <c r="N7" t="n">
-        <v>57.8</v>
+        <v>44.4</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -837,7 +841,7 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -864,30 +868,30 @@
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Magical Moonlight (IRE)</t>
+          <t>Tatianna (IRE)</t>
         </is>
       </c>
       <c r="I8" t="n">
         <v>2</v>
       </c>
       <c r="J8" t="n">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>8.6</v>
+        <v>19.6</v>
       </c>
       <c r="M8" t="n">
         <v>77.34</v>
       </c>
       <c r="N8" t="n">
-        <v>44.4</v>
+        <v>6</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -895,7 +899,7 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="9">
@@ -922,38 +926,38 @@
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Tatianna (IRE)</t>
+          <t>Granite Mountain (IRE)</t>
         </is>
       </c>
       <c r="I9" t="n">
         <v>2</v>
       </c>
       <c r="J9" t="n">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>19.6</v>
+        <v>25.1</v>
       </c>
       <c r="M9" t="n">
         <v>77.34</v>
       </c>
       <c r="N9" t="n">
-        <v>13.3</v>
+        <v>19.6</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>low</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -979,40 +983,24 @@
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
-      <c r="G10" t="n">
-        <v>8</v>
-      </c>
+      <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Granite Mountain (IRE)</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>2</v>
-      </c>
-      <c r="J10" t="n">
-        <v>126</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>25.1</v>
-      </c>
-      <c r="M10" t="n">
-        <v>77.34</v>
-      </c>
-      <c r="N10" t="n">
-        <v>25.6</v>
-      </c>
+          <t>Citrus Springs (USA)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr">
         <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="P10" t="n">
-        <v>1</v>
-      </c>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1279,7 +1267,7 @@
         <v>6</v>
       </c>
       <c r="J15" t="n">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="K15" t="n">
         <v>58</v>
@@ -1291,7 +1279,7 @@
         <v>77.06</v>
       </c>
       <c r="N15" t="n">
-        <v>30.1</v>
+        <v>23</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
@@ -1299,7 +1287,7 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="16">
@@ -1357,7 +1345,7 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1442,34 +1430,36 @@
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Girl Bear (IRE)</t>
+          <t>Stone Bear (IRE)</t>
         </is>
       </c>
       <c r="I18" t="n">
         <v>3</v>
       </c>
       <c r="J18" t="n">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="K18" t="n">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="n">
         <v>76.53</v>
       </c>
-      <c r="N18" t="inlineStr"/>
+      <c r="N18" t="n">
+        <v>80.09999999999999</v>
+      </c>
       <c r="O18" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>-9.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1496,28 +1486,30 @@
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Stone Bear (IRE)</t>
+          <t>Absoluteassignment (IRE)</t>
         </is>
       </c>
       <c r="I19" t="n">
         <v>3</v>
       </c>
       <c r="J19" t="n">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="K19" t="n">
-        <v>69</v>
-      </c>
-      <c r="L19" t="inlineStr"/>
+        <v>62</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1.25</v>
+      </c>
       <c r="M19" t="n">
         <v>76.53</v>
       </c>
       <c r="N19" t="n">
-        <v>82</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
@@ -1525,7 +1517,7 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="20">
@@ -1552,30 +1544,30 @@
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Absoluteassignment (IRE)</t>
+          <t>Reimagined (IRE)</t>
         </is>
       </c>
       <c r="I20" t="n">
         <v>3</v>
       </c>
       <c r="J20" t="n">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="K20" t="n">
-        <v>62</v>
+        <v>73</v>
       </c>
       <c r="L20" t="n">
-        <v>1.25</v>
+        <v>4</v>
       </c>
       <c r="M20" t="n">
         <v>76.53</v>
       </c>
       <c r="N20" t="n">
-        <v>69.40000000000001</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
@@ -1583,7 +1575,7 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1610,30 +1602,30 @@
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Reimagined (IRE)</t>
+          <t>Treasured Royal (IRE)</t>
         </is>
       </c>
       <c r="I21" t="n">
         <v>3</v>
       </c>
       <c r="J21" t="n">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="K21" t="n">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="L21" t="n">
-        <v>4</v>
+        <v>4.05</v>
       </c>
       <c r="M21" t="n">
         <v>76.53</v>
       </c>
       <c r="N21" t="n">
-        <v>72.40000000000001</v>
+        <v>75.2</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
@@ -1641,7 +1633,7 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -1668,30 +1660,30 @@
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Treasured Royal (IRE)</t>
+          <t>Baiana (GER)</t>
         </is>
       </c>
       <c r="I22" t="n">
         <v>3</v>
       </c>
       <c r="J22" t="n">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="K22" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="L22" t="n">
-        <v>4.05</v>
+        <v>6.55</v>
       </c>
       <c r="M22" t="n">
         <v>76.53</v>
       </c>
       <c r="N22" t="n">
-        <v>75.2</v>
+        <v>64.8</v>
       </c>
       <c r="O22" t="inlineStr">
         <is>
@@ -1699,7 +1691,7 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -1726,30 +1718,30 @@
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Baiana (GER)</t>
+          <t>Jampa Ling (IRE)</t>
         </is>
       </c>
       <c r="I23" t="n">
         <v>3</v>
       </c>
       <c r="J23" t="n">
-        <v>136</v>
+        <v>120</v>
       </c>
       <c r="K23" t="n">
-        <v>76</v>
+        <v>60</v>
       </c>
       <c r="L23" t="n">
-        <v>6.55</v>
+        <v>13.55</v>
       </c>
       <c r="M23" t="n">
         <v>76.53</v>
       </c>
       <c r="N23" t="n">
-        <v>64.8</v>
+        <v>30.1</v>
       </c>
       <c r="O23" t="inlineStr">
         <is>
@@ -1757,7 +1749,7 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="24">
@@ -1784,38 +1776,38 @@
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Jampa Ling (IRE)</t>
+          <t>Jackie Jump Up</t>
         </is>
       </c>
       <c r="I24" t="n">
         <v>3</v>
       </c>
       <c r="J24" t="n">
-        <v>120</v>
+        <v>134</v>
       </c>
       <c r="K24" t="n">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="L24" t="n">
-        <v>13.55</v>
+        <v>21.05</v>
       </c>
       <c r="M24" t="n">
         <v>76.53</v>
       </c>
       <c r="N24" t="n">
-        <v>30.1</v>
+        <v>36.8</v>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>low</t>
         </is>
       </c>
       <c r="P24" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1842,30 +1834,30 @@
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Jackie Jump Up</t>
+          <t>All Hail (IRE)</t>
         </is>
       </c>
       <c r="I25" t="n">
         <v>3</v>
       </c>
       <c r="J25" t="n">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="K25" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="L25" t="n">
-        <v>21.05</v>
+        <v>30.05</v>
       </c>
       <c r="M25" t="n">
         <v>76.53</v>
       </c>
       <c r="N25" t="n">
-        <v>36.8</v>
+        <v>25.3</v>
       </c>
       <c r="O25" t="inlineStr">
         <is>
@@ -1873,7 +1865,7 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1899,40 +1891,24 @@
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
-      <c r="G26" t="n">
-        <v>8</v>
-      </c>
+      <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr">
         <is>
-          <t>All Hail (IRE)</t>
-        </is>
-      </c>
-      <c r="I26" t="n">
-        <v>3</v>
-      </c>
-      <c r="J26" t="n">
-        <v>132</v>
-      </c>
-      <c r="K26" t="n">
-        <v>72</v>
-      </c>
-      <c r="L26" t="n">
-        <v>30.05</v>
-      </c>
-      <c r="M26" t="n">
-        <v>76.53</v>
-      </c>
-      <c r="N26" t="n">
-        <v>25.3</v>
-      </c>
+          <t>Girl Bear (IRE)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr">
         <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="P26" t="n">
-        <v>0</v>
-      </c>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2008,34 +1984,36 @@
       </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Run Forrest Run (IRE)</t>
+          <t>Are You In Or Out (IRE)</t>
         </is>
       </c>
       <c r="I28" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J28" t="n">
-        <v>124</v>
+        <v>142</v>
       </c>
       <c r="K28" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="n">
         <v>77.25</v>
       </c>
-      <c r="N28" t="inlineStr"/>
+      <c r="N28" t="n">
+        <v>73.59999999999999</v>
+      </c>
       <c r="O28" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P28" t="n">
-        <v>-20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -2062,34 +2040,38 @@
       </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Livingston Range (IRE)</t>
+          <t>Whatswrongnow (IRE)</t>
         </is>
       </c>
       <c r="I29" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J29" t="n">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="K29" t="n">
-        <v>38</v>
-      </c>
-      <c r="L29" t="inlineStr"/>
+        <v>45</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0.5</v>
+      </c>
       <c r="M29" t="n">
         <v>77.25</v>
       </c>
-      <c r="N29" t="inlineStr"/>
+      <c r="N29" t="n">
+        <v>58.4</v>
+      </c>
       <c r="O29" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P29" t="n">
-        <v>-20</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="30">
@@ -2116,34 +2098,38 @@
       </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Bel Espoir (IRE)</t>
+          <t>Happy Henry (IRE)</t>
         </is>
       </c>
       <c r="I30" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J30" t="n">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="K30" t="n">
-        <v>36</v>
-      </c>
-      <c r="L30" t="inlineStr"/>
+        <v>49</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0.53</v>
+      </c>
       <c r="M30" t="n">
         <v>77.25</v>
       </c>
-      <c r="N30" t="inlineStr"/>
+      <c r="N30" t="n">
+        <v>63.1</v>
+      </c>
       <c r="O30" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P30" t="n">
-        <v>-20</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -2170,28 +2156,30 @@
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Are You In Or Out (IRE)</t>
+          <t>Im Spartacus (IRE)</t>
         </is>
       </c>
       <c r="I31" t="n">
         <v>5</v>
       </c>
       <c r="J31" t="n">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="K31" t="n">
-        <v>60</v>
-      </c>
-      <c r="L31" t="inlineStr"/>
+        <v>53</v>
+      </c>
+      <c r="L31" t="n">
+        <v>2.28</v>
+      </c>
       <c r="M31" t="n">
         <v>77.25</v>
       </c>
       <c r="N31" t="n">
-        <v>73.59999999999999</v>
+        <v>62.9</v>
       </c>
       <c r="O31" t="inlineStr">
         <is>
@@ -2199,7 +2187,7 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2226,30 +2214,30 @@
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Whatswrongnow (IRE)</t>
+          <t>Rodeeve</t>
         </is>
       </c>
       <c r="I32" t="n">
         <v>5</v>
       </c>
       <c r="J32" t="n">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="K32" t="n">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="L32" t="n">
-        <v>0.5</v>
+        <v>2.33</v>
       </c>
       <c r="M32" t="n">
         <v>77.25</v>
       </c>
       <c r="N32" t="n">
-        <v>58.4</v>
+        <v>58.6</v>
       </c>
       <c r="O32" t="inlineStr">
         <is>
@@ -2257,7 +2245,7 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -2284,30 +2272,30 @@
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Happy Henry (IRE)</t>
+          <t>Verhoyen</t>
         </is>
       </c>
       <c r="I33" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="J33" t="n">
-        <v>131</v>
+        <v>141</v>
       </c>
       <c r="K33" t="n">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="L33" t="n">
-        <v>0.53</v>
+        <v>2.38</v>
       </c>
       <c r="M33" t="n">
         <v>77.25</v>
       </c>
       <c r="N33" t="n">
-        <v>63.1</v>
+        <v>61.8</v>
       </c>
       <c r="O33" t="inlineStr">
         <is>
@@ -2315,7 +2303,7 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34">
@@ -2342,30 +2330,30 @@
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Im Spartacus (IRE)</t>
+          <t>Jazzy Dancer (IRE)</t>
         </is>
       </c>
       <c r="I34" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J34" t="n">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="K34" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="L34" t="n">
-        <v>2.28</v>
+        <v>2.88</v>
       </c>
       <c r="M34" t="n">
         <v>77.25</v>
       </c>
       <c r="N34" t="n">
-        <v>62.9</v>
+        <v>57.2</v>
       </c>
       <c r="O34" t="inlineStr">
         <is>
@@ -2373,7 +2361,7 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -2400,30 +2388,30 @@
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Rodeeve</t>
+          <t>Reponse Finale (IRE)</t>
         </is>
       </c>
       <c r="I35" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J35" t="n">
-        <v>135</v>
+        <v>120</v>
       </c>
       <c r="K35" t="n">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="L35" t="n">
-        <v>2.33</v>
+        <v>3.38</v>
       </c>
       <c r="M35" t="n">
         <v>77.25</v>
       </c>
       <c r="N35" t="n">
-        <v>59.4</v>
+        <v>41.6</v>
       </c>
       <c r="O35" t="inlineStr">
         <is>
@@ -2458,30 +2446,30 @@
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Verhoyen</t>
+          <t>Apache Star (IRE)</t>
         </is>
       </c>
       <c r="I36" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="J36" t="n">
-        <v>141</v>
+        <v>129</v>
       </c>
       <c r="K36" t="n">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="L36" t="n">
-        <v>2.38</v>
+        <v>7.88</v>
       </c>
       <c r="M36" t="n">
         <v>77.25</v>
       </c>
       <c r="N36" t="n">
-        <v>61.8</v>
+        <v>37.4</v>
       </c>
       <c r="O36" t="inlineStr">
         <is>
@@ -2489,7 +2477,7 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="37">
@@ -2516,30 +2504,30 @@
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="n">
+        <v>10</v>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Jackandthefox (IRE)</t>
+        </is>
+      </c>
+      <c r="I37" t="n">
         <v>7</v>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Jazzy Dancer (IRE)</t>
-        </is>
-      </c>
-      <c r="I37" t="n">
-        <v>8</v>
-      </c>
       <c r="J37" t="n">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="K37" t="n">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="L37" t="n">
-        <v>2.88</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="M37" t="n">
         <v>77.25</v>
       </c>
       <c r="N37" t="n">
-        <v>57.2</v>
+        <v>32.9</v>
       </c>
       <c r="O37" t="inlineStr">
         <is>
@@ -2547,7 +2535,7 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="38">
@@ -2574,30 +2562,30 @@
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Reponse Finale (IRE)</t>
+          <t>El Fontenaro (IRE)</t>
         </is>
       </c>
       <c r="I38" t="n">
         <v>4</v>
       </c>
       <c r="J38" t="n">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="K38" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="L38" t="n">
-        <v>3.38</v>
+        <v>9.23</v>
       </c>
       <c r="M38" t="n">
         <v>77.25</v>
       </c>
       <c r="N38" t="n">
-        <v>49.9</v>
+        <v>38.1</v>
       </c>
       <c r="O38" t="inlineStr">
         <is>
@@ -2605,7 +2593,7 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="39">
@@ -2632,30 +2620,30 @@
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Apache Star (IRE)</t>
+          <t>Oxford Circus (IRE)</t>
         </is>
       </c>
       <c r="I39" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J39" t="n">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="K39" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="L39" t="n">
-        <v>7.88</v>
+        <v>9.33</v>
       </c>
       <c r="M39" t="n">
         <v>77.25</v>
       </c>
       <c r="N39" t="n">
-        <v>37.4</v>
+        <v>30.9</v>
       </c>
       <c r="O39" t="inlineStr">
         <is>
@@ -2663,7 +2651,7 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="40">
@@ -2690,30 +2678,30 @@
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Jackandthefox (IRE)</t>
+          <t>Son Of Wind (IRE)</t>
         </is>
       </c>
       <c r="I40" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J40" t="n">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="K40" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="L40" t="n">
-        <v>9.129999999999999</v>
+        <v>12.33</v>
       </c>
       <c r="M40" t="n">
         <v>77.25</v>
       </c>
       <c r="N40" t="n">
-        <v>32.9</v>
+        <v>28.3</v>
       </c>
       <c r="O40" t="inlineStr">
         <is>
@@ -2721,7 +2709,7 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="41">
@@ -2748,30 +2736,30 @@
       </c>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>El Fontenaro (IRE)</t>
+          <t>Rattletheonionbag (IRE)</t>
         </is>
       </c>
       <c r="I41" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J41" t="n">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="K41" t="n">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="L41" t="n">
-        <v>9.23</v>
+        <v>12.48</v>
       </c>
       <c r="M41" t="n">
         <v>77.25</v>
       </c>
       <c r="N41" t="n">
-        <v>38.1</v>
+        <v>16.6</v>
       </c>
       <c r="O41" t="inlineStr">
         <is>
@@ -2779,7 +2767,7 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="42">
@@ -2806,30 +2794,30 @@
       </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Oxford Circus (IRE)</t>
+          <t>Harry Longabaugh (IRE)</t>
         </is>
       </c>
       <c r="I42" t="n">
         <v>4</v>
       </c>
       <c r="J42" t="n">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="K42" t="n">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="L42" t="n">
-        <v>9.33</v>
+        <v>13.48</v>
       </c>
       <c r="M42" t="n">
         <v>77.25</v>
       </c>
       <c r="N42" t="n">
-        <v>40.4</v>
+        <v>31.2</v>
       </c>
       <c r="O42" t="inlineStr">
         <is>
@@ -2864,30 +2852,30 @@
       </c>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Son Of Wind (IRE)</t>
+          <t>Miqdaad (IRE)</t>
         </is>
       </c>
       <c r="I43" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J43" t="n">
-        <v>132</v>
+        <v>121</v>
       </c>
       <c r="K43" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="L43" t="n">
-        <v>12.33</v>
+        <v>16.48</v>
       </c>
       <c r="M43" t="n">
         <v>77.25</v>
       </c>
       <c r="N43" t="n">
-        <v>28.3</v>
+        <v>-1.3</v>
       </c>
       <c r="O43" t="inlineStr">
         <is>
@@ -2895,7 +2883,7 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="44">
@@ -2922,38 +2910,38 @@
       </c>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Rattletheonionbag (IRE)</t>
+          <t>Twotolose (IRE)</t>
         </is>
       </c>
       <c r="I44" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J44" t="n">
-        <v>122</v>
+        <v>137</v>
       </c>
       <c r="K44" t="n">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="L44" t="n">
-        <v>12.48</v>
+        <v>21.48</v>
       </c>
       <c r="M44" t="n">
         <v>77.25</v>
       </c>
       <c r="N44" t="n">
-        <v>16.6</v>
+        <v>24.6</v>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>low</t>
         </is>
       </c>
       <c r="P44" t="n">
-        <v>-3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2980,38 +2968,38 @@
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Harry Longabaugh (IRE)</t>
+          <t>Green Icon (FR)</t>
         </is>
       </c>
       <c r="I45" t="n">
         <v>4</v>
       </c>
       <c r="J45" t="n">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="K45" t="n">
         <v>59</v>
       </c>
       <c r="L45" t="n">
-        <v>13.48</v>
+        <v>22.48</v>
       </c>
       <c r="M45" t="n">
         <v>77.25</v>
       </c>
       <c r="N45" t="n">
-        <v>31.2</v>
+        <v>26.4</v>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>low</t>
         </is>
       </c>
       <c r="P45" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="46">
@@ -3037,40 +3025,24 @@
         </is>
       </c>
       <c r="F46" t="inlineStr"/>
-      <c r="G46" t="n">
-        <v>16</v>
-      </c>
+      <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Miqdaad (IRE)</t>
-        </is>
-      </c>
-      <c r="I46" t="n">
-        <v>6</v>
-      </c>
-      <c r="J46" t="n">
-        <v>124</v>
-      </c>
-      <c r="K46" t="n">
-        <v>42</v>
-      </c>
-      <c r="L46" t="n">
-        <v>16.48</v>
-      </c>
-      <c r="M46" t="n">
-        <v>77.25</v>
-      </c>
-      <c r="N46" t="n">
-        <v>0.1</v>
-      </c>
+          <t>Run Forrest Run (IRE)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
       <c r="O46" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="P46" t="n">
-        <v>-2</v>
-      </c>
+      <c r="P46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -3095,40 +3067,24 @@
         </is>
       </c>
       <c r="F47" t="inlineStr"/>
-      <c r="G47" t="n">
-        <v>17</v>
-      </c>
+      <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Twotolose (IRE)</t>
-        </is>
-      </c>
-      <c r="I47" t="n">
-        <v>5</v>
-      </c>
-      <c r="J47" t="n">
-        <v>137</v>
-      </c>
-      <c r="K47" t="n">
-        <v>55</v>
-      </c>
-      <c r="L47" t="n">
-        <v>21.48</v>
-      </c>
-      <c r="M47" t="n">
-        <v>77.25</v>
-      </c>
-      <c r="N47" t="n">
-        <v>24.6</v>
-      </c>
+          <t>Bel Espoir (IRE)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
       <c r="O47" t="inlineStr">
         <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="P47" t="n">
-        <v>1</v>
-      </c>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -3153,40 +3109,24 @@
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
-      <c r="G48" t="n">
-        <v>18</v>
-      </c>
+      <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Green Icon (FR)</t>
-        </is>
-      </c>
-      <c r="I48" t="n">
-        <v>4</v>
-      </c>
-      <c r="J48" t="n">
-        <v>142</v>
-      </c>
-      <c r="K48" t="n">
-        <v>59</v>
-      </c>
-      <c r="L48" t="n">
-        <v>22.48</v>
-      </c>
-      <c r="M48" t="n">
-        <v>77.25</v>
-      </c>
-      <c r="N48" t="n">
-        <v>26.4</v>
-      </c>
+          <t>Livingston Range (IRE)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
       <c r="O48" t="inlineStr">
         <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="P48" t="n">
-        <v>3</v>
-      </c>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -3337,7 +3277,7 @@
         <v>3</v>
       </c>
       <c r="J51" t="n">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="K51" t="n">
         <v>72</v>
@@ -3349,7 +3289,7 @@
         <v>90.81</v>
       </c>
       <c r="N51" t="n">
-        <v>66.8</v>
+        <v>62.7</v>
       </c>
       <c r="O51" t="inlineStr">
         <is>
@@ -3453,7 +3393,7 @@
         <v>3</v>
       </c>
       <c r="J53" t="n">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="K53" t="n">
         <v>60</v>
@@ -3465,7 +3405,7 @@
         <v>90.81</v>
       </c>
       <c r="N53" t="n">
-        <v>53.7</v>
+        <v>47</v>
       </c>
       <c r="O53" t="inlineStr">
         <is>
@@ -3473,7 +3413,7 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="54">
@@ -3531,7 +3471,7 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -3569,7 +3509,7 @@
         <v>3</v>
       </c>
       <c r="J55" t="n">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="K55" t="n">
         <v>53</v>
@@ -3581,7 +3521,7 @@
         <v>90.81</v>
       </c>
       <c r="N55" t="n">
-        <v>35.7</v>
+        <v>31.7</v>
       </c>
       <c r="O55" t="inlineStr">
         <is>
@@ -3685,7 +3625,7 @@
         <v>3</v>
       </c>
       <c r="J57" t="n">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="K57" t="n">
         <v>62</v>
@@ -3697,7 +3637,7 @@
         <v>90.81</v>
       </c>
       <c r="N57" t="n">
-        <v>26.3</v>
+        <v>22</v>
       </c>
       <c r="O57" t="inlineStr">
         <is>
@@ -3975,7 +3915,7 @@
         <v>5</v>
       </c>
       <c r="J62" t="n">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="K62" t="n">
         <v>60</v>
@@ -3985,7 +3925,7 @@
         <v>131.52</v>
       </c>
       <c r="N62" t="n">
-        <v>56.5</v>
+        <v>49.6</v>
       </c>
       <c r="O62" t="inlineStr">
         <is>
@@ -3993,7 +3933,7 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="63">
@@ -4051,7 +3991,7 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -4089,7 +4029,7 @@
         <v>4</v>
       </c>
       <c r="J64" t="n">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="K64" t="n">
         <v>58</v>
@@ -4101,7 +4041,7 @@
         <v>131.52</v>
       </c>
       <c r="N64" t="n">
-        <v>47.2</v>
+        <v>41</v>
       </c>
       <c r="O64" t="inlineStr">
         <is>
@@ -4109,7 +4049,7 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>-1.5</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="65">
@@ -4205,7 +4145,7 @@
         <v>6</v>
       </c>
       <c r="J66" t="n">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="K66" t="n">
         <v>62</v>
@@ -4217,7 +4157,7 @@
         <v>131.52</v>
       </c>
       <c r="N66" t="n">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="O66" t="inlineStr">
         <is>
@@ -4225,7 +4165,7 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="67">
@@ -4263,7 +4203,7 @@
         <v>4</v>
       </c>
       <c r="J67" t="n">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="K67" t="n">
         <v>69</v>
@@ -4275,7 +4215,7 @@
         <v>131.52</v>
       </c>
       <c r="N67" t="n">
-        <v>47.2</v>
+        <v>45</v>
       </c>
       <c r="O67" t="inlineStr">
         <is>
@@ -4283,7 +4223,7 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="68">
@@ -4321,7 +4261,7 @@
         <v>5</v>
       </c>
       <c r="J68" t="n">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="K68" t="n">
         <v>67</v>
@@ -4333,7 +4273,7 @@
         <v>131.52</v>
       </c>
       <c r="N68" t="n">
-        <v>39.8</v>
+        <v>35.3</v>
       </c>
       <c r="O68" t="inlineStr">
         <is>
@@ -4341,7 +4281,7 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="69">
@@ -4379,7 +4319,7 @@
         <v>4</v>
       </c>
       <c r="J69" t="n">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="K69" t="n">
         <v>64</v>
@@ -4391,7 +4331,7 @@
         <v>131.52</v>
       </c>
       <c r="N69" t="n">
-        <v>38</v>
+        <v>36.5</v>
       </c>
       <c r="O69" t="inlineStr">
         <is>
@@ -4399,7 +4339,7 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -4437,7 +4377,7 @@
         <v>6</v>
       </c>
       <c r="J70" t="n">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="K70" t="n">
         <v>49</v>
@@ -4449,7 +4389,7 @@
         <v>131.52</v>
       </c>
       <c r="N70" t="n">
-        <v>23.8</v>
+        <v>18.7</v>
       </c>
       <c r="O70" t="inlineStr">
         <is>
@@ -4457,7 +4397,7 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>-4</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="71">
@@ -4515,7 +4455,7 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="72">
@@ -4573,7 +4513,7 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="73">
@@ -4611,7 +4551,7 @@
         <v>4</v>
       </c>
       <c r="J73" t="n">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="K73" t="n">
         <v>68</v>
@@ -4623,7 +4563,7 @@
         <v>131.52</v>
       </c>
       <c r="N73" t="n">
-        <v>33.2</v>
+        <v>31.5</v>
       </c>
       <c r="O73" t="inlineStr">
         <is>
@@ -4669,7 +4609,7 @@
         <v>6</v>
       </c>
       <c r="J74" t="n">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="K74" t="n">
         <v>72</v>
@@ -4681,7 +4621,7 @@
         <v>131.52</v>
       </c>
       <c r="N74" t="n">
-        <v>29.4</v>
+        <v>27.2</v>
       </c>
       <c r="O74" t="inlineStr">
         <is>
@@ -4689,7 +4629,7 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="75">
@@ -4727,7 +4667,7 @@
         <v>4</v>
       </c>
       <c r="J75" t="n">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="K75" t="n">
         <v>62</v>
@@ -4739,7 +4679,7 @@
         <v>131.52</v>
       </c>
       <c r="N75" t="n">
-        <v>21.5</v>
+        <v>18</v>
       </c>
       <c r="O75" t="inlineStr">
         <is>
@@ -4747,7 +4687,7 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="76">
@@ -4785,7 +4725,7 @@
         <v>4</v>
       </c>
       <c r="J76" t="n">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="K76" t="n">
         <v>62</v>
@@ -4797,7 +4737,7 @@
         <v>131.52</v>
       </c>
       <c r="N76" t="n">
-        <v>-23.7</v>
+        <v>25.3</v>
       </c>
       <c r="O76" t="inlineStr">
         <is>
@@ -4805,7 +4745,7 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="77">
@@ -4841,7 +4781,7 @@
         <v>6</v>
       </c>
       <c r="J77" t="n">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="K77" t="n">
         <v>70</v>
@@ -5706,34 +5646,36 @@
         <v>6</v>
       </c>
       <c r="G92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Contemplation</t>
+          <t>Vegas Virtue (IRE)</t>
         </is>
       </c>
       <c r="I92" t="n">
         <v>3</v>
       </c>
       <c r="J92" t="n">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="K92" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="L92" t="inlineStr"/>
       <c r="M92" t="n">
         <v>102.43</v>
       </c>
-      <c r="N92" t="inlineStr"/>
+      <c r="N92" t="n">
+        <v>72.90000000000001</v>
+      </c>
       <c r="O92" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P92" t="n">
-        <v>-10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93">
@@ -5762,11 +5704,11 @@
         <v>6</v>
       </c>
       <c r="G93" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Vegas Virtue (IRE)</t>
+          <t>Thats Enough</t>
         </is>
       </c>
       <c r="I93" t="n">
@@ -5778,12 +5720,14 @@
       <c r="K93" t="n">
         <v>55</v>
       </c>
-      <c r="L93" t="inlineStr"/>
+      <c r="L93" t="n">
+        <v>0.15</v>
+      </c>
       <c r="M93" t="n">
         <v>102.43</v>
       </c>
       <c r="N93" t="n">
-        <v>72.90000000000001</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="O93" t="inlineStr">
         <is>
@@ -5820,30 +5764,30 @@
         <v>6</v>
       </c>
       <c r="G94" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Thats Enough</t>
+          <t>Hood Wink</t>
         </is>
       </c>
       <c r="I94" t="n">
         <v>3</v>
       </c>
       <c r="J94" t="n">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="K94" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="L94" t="n">
-        <v>0.15</v>
+        <v>0.9</v>
       </c>
       <c r="M94" t="n">
         <v>102.43</v>
       </c>
       <c r="N94" t="n">
-        <v>72.09999999999999</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="O94" t="inlineStr">
         <is>
@@ -5880,30 +5824,30 @@
         <v>6</v>
       </c>
       <c r="G95" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Hood Wink</t>
+          <t>Crystal Aurora (IRE)</t>
         </is>
       </c>
       <c r="I95" t="n">
         <v>3</v>
       </c>
       <c r="J95" t="n">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="K95" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="L95" t="n">
-        <v>0.9</v>
+        <v>4.4</v>
       </c>
       <c r="M95" t="n">
         <v>102.43</v>
       </c>
       <c r="N95" t="n">
-        <v>66.90000000000001</v>
+        <v>62.9</v>
       </c>
       <c r="O95" t="inlineStr">
         <is>
@@ -5940,30 +5884,30 @@
         <v>6</v>
       </c>
       <c r="G96" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Crystal Aurora (IRE)</t>
+          <t>Regal Knight</t>
         </is>
       </c>
       <c r="I96" t="n">
         <v>3</v>
       </c>
       <c r="J96" t="n">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="K96" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="L96" t="n">
-        <v>4.4</v>
+        <v>4.45</v>
       </c>
       <c r="M96" t="n">
         <v>102.43</v>
       </c>
       <c r="N96" t="n">
-        <v>62.9</v>
+        <v>56.3</v>
       </c>
       <c r="O96" t="inlineStr">
         <is>
@@ -5971,7 +5915,7 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="97">
@@ -6000,30 +5944,30 @@
         <v>6</v>
       </c>
       <c r="G97" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Regal Knight</t>
+          <t>Harswell River (IRE)</t>
         </is>
       </c>
       <c r="I97" t="n">
         <v>3</v>
       </c>
       <c r="J97" t="n">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="K97" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="L97" t="n">
-        <v>4.45</v>
+        <v>4.95</v>
       </c>
       <c r="M97" t="n">
         <v>102.43</v>
       </c>
       <c r="N97" t="n">
-        <v>56.3</v>
+        <v>58.2</v>
       </c>
       <c r="O97" t="inlineStr">
         <is>
@@ -6031,7 +5975,7 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="98">
@@ -6060,30 +6004,30 @@
         <v>6</v>
       </c>
       <c r="G98" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Harswell River (IRE)</t>
+          <t>Eva The Deeva</t>
         </is>
       </c>
       <c r="I98" t="n">
         <v>3</v>
       </c>
       <c r="J98" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="K98" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="L98" t="n">
-        <v>4.95</v>
+        <v>6.2</v>
       </c>
       <c r="M98" t="n">
         <v>102.43</v>
       </c>
       <c r="N98" t="n">
-        <v>58.2</v>
+        <v>52.2</v>
       </c>
       <c r="O98" t="inlineStr">
         <is>
@@ -6091,7 +6035,7 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99">
@@ -6120,11 +6064,11 @@
         <v>6</v>
       </c>
       <c r="G99" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Eva The Deeva</t>
+          <t>Captain Bruce (IRE)</t>
         </is>
       </c>
       <c r="I99" t="n">
@@ -6137,17 +6081,17 @@
         <v>50</v>
       </c>
       <c r="L99" t="n">
-        <v>6.2</v>
+        <v>21.2</v>
       </c>
       <c r="M99" t="n">
         <v>102.43</v>
       </c>
       <c r="N99" t="n">
-        <v>52.2</v>
+        <v>33.9</v>
       </c>
       <c r="O99" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>low</t>
         </is>
       </c>
       <c r="P99" t="n">
@@ -6180,30 +6124,30 @@
         <v>6</v>
       </c>
       <c r="G100" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Captain Bruce (IRE)</t>
+          <t>Wondrous (IRE)</t>
         </is>
       </c>
       <c r="I100" t="n">
         <v>3</v>
       </c>
       <c r="J100" t="n">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="K100" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="L100" t="n">
-        <v>21.2</v>
+        <v>38.2</v>
       </c>
       <c r="M100" t="n">
         <v>102.43</v>
       </c>
       <c r="N100" t="n">
-        <v>33.9</v>
+        <v>13.7</v>
       </c>
       <c r="O100" t="inlineStr">
         <is>
@@ -6239,40 +6183,24 @@
       <c r="F101" t="n">
         <v>6</v>
       </c>
-      <c r="G101" t="n">
-        <v>9</v>
-      </c>
+      <c r="G101" t="inlineStr"/>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Wondrous (IRE)</t>
-        </is>
-      </c>
-      <c r="I101" t="n">
-        <v>3</v>
-      </c>
-      <c r="J101" t="n">
-        <v>132</v>
-      </c>
-      <c r="K101" t="n">
-        <v>52</v>
-      </c>
-      <c r="L101" t="n">
-        <v>38.2</v>
-      </c>
-      <c r="M101" t="n">
-        <v>102.43</v>
-      </c>
-      <c r="N101" t="n">
-        <v>13.7</v>
-      </c>
+          <t>Contemplation</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr"/>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr"/>
+      <c r="M101" t="inlineStr"/>
+      <c r="N101" t="inlineStr"/>
       <c r="O101" t="inlineStr">
         <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="P101" t="n">
-        <v>0</v>
-      </c>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -7267,7 +7195,7 @@
         <v>4</v>
       </c>
       <c r="J118" t="n">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="K118" t="n">
         <v>91</v>
@@ -7279,7 +7207,7 @@
         <v>123.27</v>
       </c>
       <c r="N118" t="n">
-        <v>68.40000000000001</v>
+        <v>63.6</v>
       </c>
       <c r="O118" t="inlineStr">
         <is>
@@ -7556,34 +7484,36 @@
         <v>6</v>
       </c>
       <c r="G123" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Solar Biricz (IRE)</t>
+          <t>Jet Warrior</t>
         </is>
       </c>
       <c r="I123" t="n">
         <v>4</v>
       </c>
       <c r="J123" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="K123" t="n">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="L123" t="inlineStr"/>
       <c r="M123" t="n">
         <v>71.95999999999999</v>
       </c>
-      <c r="N123" t="inlineStr"/>
+      <c r="N123" t="n">
+        <v>83.7</v>
+      </c>
       <c r="O123" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P123" t="n">
-        <v>-9.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="124">
@@ -7612,34 +7542,38 @@
         <v>6</v>
       </c>
       <c r="G124" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Golden Prosperity (IRE)</t>
+          <t>Angel Of England</t>
         </is>
       </c>
       <c r="I124" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J124" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="K124" t="n">
-        <v>52</v>
-      </c>
-      <c r="L124" t="inlineStr"/>
+        <v>51</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.5</v>
+      </c>
       <c r="M124" t="n">
         <v>71.95999999999999</v>
       </c>
-      <c r="N124" t="inlineStr"/>
+      <c r="N124" t="n">
+        <v>74.2</v>
+      </c>
       <c r="O124" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P124" t="n">
-        <v>-9.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="125">
@@ -7668,28 +7602,30 @@
         <v>6</v>
       </c>
       <c r="G125" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Jet Warrior</t>
+          <t>Ridgemaster (IRE)</t>
         </is>
       </c>
       <c r="I125" t="n">
         <v>4</v>
       </c>
       <c r="J125" t="n">
-        <v>140</v>
+        <v>127</v>
       </c>
       <c r="K125" t="n">
-        <v>59</v>
-      </c>
-      <c r="L125" t="inlineStr"/>
+        <v>49</v>
+      </c>
+      <c r="L125" t="n">
+        <v>1.75</v>
+      </c>
       <c r="M125" t="n">
         <v>71.95999999999999</v>
       </c>
       <c r="N125" t="n">
-        <v>83.7</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="O125" t="inlineStr">
         <is>
@@ -7697,7 +7633,7 @@
         </is>
       </c>
       <c r="P125" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="126">
@@ -7726,30 +7662,30 @@
         <v>6</v>
       </c>
       <c r="G126" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Angel Of England</t>
+          <t>Night Emperor (IRE)</t>
         </is>
       </c>
       <c r="I126" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J126" t="n">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="K126" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="L126" t="n">
-        <v>0.5</v>
+        <v>2.5</v>
       </c>
       <c r="M126" t="n">
         <v>71.95999999999999</v>
       </c>
       <c r="N126" t="n">
-        <v>74.2</v>
+        <v>69.8</v>
       </c>
       <c r="O126" t="inlineStr">
         <is>
@@ -7757,7 +7693,7 @@
         </is>
       </c>
       <c r="P126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="127">
@@ -7786,30 +7722,30 @@
         <v>6</v>
       </c>
       <c r="G127" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Ridgemaster (IRE)</t>
+          <t>Tickets</t>
         </is>
       </c>
       <c r="I127" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J127" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="K127" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="L127" t="n">
-        <v>1.75</v>
+        <v>3.25</v>
       </c>
       <c r="M127" t="n">
         <v>71.95999999999999</v>
       </c>
       <c r="N127" t="n">
-        <v>69.7</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="O127" t="inlineStr">
         <is>
@@ -7817,7 +7753,7 @@
         </is>
       </c>
       <c r="P127" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="128">
@@ -7846,30 +7782,30 @@
         <v>6</v>
       </c>
       <c r="G128" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Night Emperor (IRE)</t>
+          <t>Hurstwood</t>
         </is>
       </c>
       <c r="I128" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="J128" t="n">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="K128" t="n">
         <v>53</v>
       </c>
       <c r="L128" t="n">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="M128" t="n">
         <v>71.95999999999999</v>
       </c>
       <c r="N128" t="n">
-        <v>69.8</v>
+        <v>60.6</v>
       </c>
       <c r="O128" t="inlineStr">
         <is>
@@ -7877,7 +7813,7 @@
         </is>
       </c>
       <c r="P128" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="129">
@@ -7906,30 +7842,30 @@
         <v>6</v>
       </c>
       <c r="G129" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Tickets</t>
+          <t>Tarlac (IRE)</t>
         </is>
       </c>
       <c r="I129" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J129" t="n">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="K129" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="L129" t="n">
-        <v>3.25</v>
+        <v>4.5</v>
       </c>
       <c r="M129" t="n">
         <v>71.95999999999999</v>
       </c>
       <c r="N129" t="n">
-        <v>65.09999999999999</v>
+        <v>58.3</v>
       </c>
       <c r="O129" t="inlineStr">
         <is>
@@ -7937,7 +7873,7 @@
         </is>
       </c>
       <c r="P129" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="130">
@@ -7966,15 +7902,15 @@
         <v>6</v>
       </c>
       <c r="G130" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Hurstwood</t>
+          <t>Barmyblade (IRE)</t>
         </is>
       </c>
       <c r="I130" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="J130" t="n">
         <v>134</v>
@@ -7983,13 +7919,13 @@
         <v>53</v>
       </c>
       <c r="L130" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M130" t="n">
         <v>71.95999999999999</v>
       </c>
       <c r="N130" t="n">
-        <v>63.6</v>
+        <v>58.6</v>
       </c>
       <c r="O130" t="inlineStr">
         <is>
@@ -7997,7 +7933,7 @@
         </is>
       </c>
       <c r="P130" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="131">
@@ -8025,40 +7961,24 @@
       <c r="F131" t="n">
         <v>6</v>
       </c>
-      <c r="G131" t="n">
-        <v>7</v>
-      </c>
+      <c r="G131" t="inlineStr"/>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Tarlac (IRE)</t>
-        </is>
-      </c>
-      <c r="I131" t="n">
-        <v>4</v>
-      </c>
-      <c r="J131" t="n">
-        <v>134</v>
-      </c>
-      <c r="K131" t="n">
-        <v>53</v>
-      </c>
-      <c r="L131" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="M131" t="n">
-        <v>71.95999999999999</v>
-      </c>
-      <c r="N131" t="n">
-        <v>63.5</v>
-      </c>
+          <t>Solar Biricz (IRE)</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr"/>
+      <c r="J131" t="inlineStr"/>
+      <c r="K131" t="inlineStr"/>
+      <c r="L131" t="inlineStr"/>
+      <c r="M131" t="inlineStr"/>
+      <c r="N131" t="inlineStr"/>
       <c r="O131" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="P131" t="n">
-        <v>0</v>
-      </c>
+      <c r="P131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -8085,40 +8005,24 @@
       <c r="F132" t="n">
         <v>6</v>
       </c>
-      <c r="G132" t="n">
-        <v>8</v>
-      </c>
+      <c r="G132" t="inlineStr"/>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Barmyblade (IRE)</t>
-        </is>
-      </c>
-      <c r="I132" t="n">
-        <v>4</v>
-      </c>
-      <c r="J132" t="n">
-        <v>134</v>
-      </c>
-      <c r="K132" t="n">
-        <v>53</v>
-      </c>
-      <c r="L132" t="n">
-        <v>6</v>
-      </c>
-      <c r="M132" t="n">
-        <v>71.95999999999999</v>
-      </c>
-      <c r="N132" t="n">
-        <v>58.6</v>
-      </c>
+          <t>Golden Prosperity (IRE)</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr"/>
+      <c r="J132" t="inlineStr"/>
+      <c r="K132" t="inlineStr"/>
+      <c r="L132" t="inlineStr"/>
+      <c r="M132" t="inlineStr"/>
+      <c r="N132" t="inlineStr"/>
       <c r="O132" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="P132" t="n">
-        <v>0</v>
-      </c>
+      <c r="P132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -8573,7 +8477,7 @@
         <v>4</v>
       </c>
       <c r="J140" t="n">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="K140" t="n">
         <v>70</v>
@@ -8585,7 +8489,7 @@
         <v>58.88</v>
       </c>
       <c r="N140" t="n">
-        <v>74.59999999999999</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="O140" t="inlineStr">
         <is>
@@ -8593,7 +8497,7 @@
         </is>
       </c>
       <c r="P140" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="141">
@@ -8653,7 +8557,7 @@
         </is>
       </c>
       <c r="P141" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="142">
@@ -8713,7 +8617,7 @@
         </is>
       </c>
       <c r="P142" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="143">
@@ -8813,7 +8717,7 @@
         <v>5</v>
       </c>
       <c r="J144" t="n">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="K144" t="n">
         <v>68</v>
@@ -8825,7 +8729,7 @@
         <v>58.88</v>
       </c>
       <c r="N144" t="n">
-        <v>63.2</v>
+        <v>58.5</v>
       </c>
       <c r="O144" t="inlineStr">
         <is>
@@ -8833,7 +8737,7 @@
         </is>
       </c>
       <c r="P144" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="145">
@@ -9775,7 +9679,7 @@
         <v>0</v>
       </c>
       <c r="L160" t="n">
-        <v>5.8</v>
+        <v>5.800000000000001</v>
       </c>
       <c r="M160" t="n">
         <v>62.33</v>
@@ -9878,34 +9782,36 @@
         <v>1</v>
       </c>
       <c r="G162" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>Beylerbeyi</t>
+          <t>Dubai Future</t>
         </is>
       </c>
       <c r="I162" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J162" t="n">
         <v>130</v>
       </c>
       <c r="K162" t="n">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="L162" t="inlineStr"/>
       <c r="M162" t="n">
         <v>219.9</v>
       </c>
-      <c r="N162" t="inlineStr"/>
+      <c r="N162" t="n">
+        <v>40.4</v>
+      </c>
       <c r="O162" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>provisional</t>
         </is>
       </c>
       <c r="P162" t="n">
-        <v>-8</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="163">
@@ -9934,28 +9840,30 @@
         <v>1</v>
       </c>
       <c r="G163" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>Dubai Future</t>
+          <t>Sweet William (IRE)</t>
         </is>
       </c>
       <c r="I163" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J163" t="n">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="K163" t="n">
-        <v>109</v>
-      </c>
-      <c r="L163" t="inlineStr"/>
+        <v>117</v>
+      </c>
+      <c r="L163" t="n">
+        <v>0.15</v>
+      </c>
       <c r="M163" t="n">
         <v>219.9</v>
       </c>
       <c r="N163" t="n">
-        <v>40.4</v>
+        <v>52.8</v>
       </c>
       <c r="O163" t="inlineStr">
         <is>
@@ -9963,7 +9871,7 @@
         </is>
       </c>
       <c r="P163" t="n">
-        <v>-4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="164">
@@ -9992,30 +9900,30 @@
         <v>1</v>
       </c>
       <c r="G164" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>Sweet William (IRE)</t>
+          <t>Lazy Griff (GER)</t>
         </is>
       </c>
       <c r="I164" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J164" t="n">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="K164" t="n">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="L164" t="n">
-        <v>0.15</v>
+        <v>1.9</v>
       </c>
       <c r="M164" t="n">
         <v>219.9</v>
       </c>
       <c r="N164" t="n">
-        <v>52.8</v>
+        <v>44.1</v>
       </c>
       <c r="O164" t="inlineStr">
         <is>
@@ -10052,30 +9960,30 @@
         <v>1</v>
       </c>
       <c r="G165" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Lazy Griff (GER)</t>
+          <t>Epic Poet (IRE)</t>
         </is>
       </c>
       <c r="I165" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J165" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="K165" t="n">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="L165" t="n">
-        <v>1.9</v>
+        <v>2.65</v>
       </c>
       <c r="M165" t="n">
         <v>219.9</v>
       </c>
       <c r="N165" t="n">
-        <v>44.1</v>
+        <v>43.1</v>
       </c>
       <c r="O165" t="inlineStr">
         <is>
@@ -10112,11 +10020,11 @@
         <v>1</v>
       </c>
       <c r="G166" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Epic Poet (IRE)</t>
+          <t>Paradias (GER)</t>
         </is>
       </c>
       <c r="I166" t="n">
@@ -10126,16 +10034,16 @@
         <v>130</v>
       </c>
       <c r="K166" t="n">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="L166" t="n">
-        <v>2.65</v>
+        <v>4.65</v>
       </c>
       <c r="M166" t="n">
         <v>219.9</v>
       </c>
       <c r="N166" t="n">
-        <v>43.1</v>
+        <v>39.7</v>
       </c>
       <c r="O166" t="inlineStr">
         <is>
@@ -10143,7 +10051,7 @@
         </is>
       </c>
       <c r="P166" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="167">
@@ -10172,30 +10080,30 @@
         <v>1</v>
       </c>
       <c r="G167" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>Paradias (GER)</t>
+          <t>Furthur (IRE)</t>
         </is>
       </c>
       <c r="I167" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J167" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="K167" t="n">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="L167" t="n">
-        <v>4.65</v>
+        <v>4.8</v>
       </c>
       <c r="M167" t="n">
         <v>219.9</v>
       </c>
       <c r="N167" t="n">
-        <v>39.7</v>
+        <v>40.7</v>
       </c>
       <c r="O167" t="inlineStr">
         <is>
@@ -10203,7 +10111,7 @@
         </is>
       </c>
       <c r="P167" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="168">
@@ -10232,30 +10140,30 @@
         <v>1</v>
       </c>
       <c r="G168" t="n">
+        <v>7</v>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>Duke Of Oxford</t>
+        </is>
+      </c>
+      <c r="I168" t="n">
         <v>6</v>
       </c>
-      <c r="H168" t="inlineStr">
-        <is>
-          <t>Furthur (IRE)</t>
-        </is>
-      </c>
-      <c r="I168" t="n">
-        <v>4</v>
-      </c>
       <c r="J168" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="K168" t="n">
-        <v>111</v>
+        <v>102</v>
       </c>
       <c r="L168" t="n">
-        <v>4.8</v>
+        <v>5.55</v>
       </c>
       <c r="M168" t="n">
         <v>219.9</v>
       </c>
       <c r="N168" t="n">
-        <v>40.7</v>
+        <v>37.5</v>
       </c>
       <c r="O168" t="inlineStr">
         <is>
@@ -10263,7 +10171,7 @@
         </is>
       </c>
       <c r="P168" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="169">
@@ -10291,40 +10199,24 @@
       <c r="F169" t="n">
         <v>1</v>
       </c>
-      <c r="G169" t="n">
-        <v>7</v>
-      </c>
+      <c r="G169" t="inlineStr"/>
       <c r="H169" t="inlineStr">
         <is>
-          <t>Duke Of Oxford</t>
-        </is>
-      </c>
-      <c r="I169" t="n">
-        <v>6</v>
-      </c>
-      <c r="J169" t="n">
-        <v>130</v>
-      </c>
-      <c r="K169" t="n">
-        <v>102</v>
-      </c>
-      <c r="L169" t="n">
-        <v>5.55</v>
-      </c>
-      <c r="M169" t="n">
-        <v>219.9</v>
-      </c>
-      <c r="N169" t="n">
-        <v>37.5</v>
-      </c>
+          <t>Beylerbeyi</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr"/>
+      <c r="J169" t="inlineStr"/>
+      <c r="K169" t="inlineStr"/>
+      <c r="L169" t="inlineStr"/>
+      <c r="M169" t="inlineStr"/>
+      <c r="N169" t="inlineStr"/>
       <c r="O169" t="inlineStr">
         <is>
-          <t>provisional</t>
-        </is>
-      </c>
-      <c r="P169" t="n">
-        <v>0</v>
-      </c>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -10352,11 +10244,11 @@
         <v>1</v>
       </c>
       <c r="G170" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>Padraig Dawn (IRE)</t>
+          <t>Talk Of New York</t>
         </is>
       </c>
       <c r="I170" t="n">
@@ -10366,20 +10258,22 @@
         <v>128</v>
       </c>
       <c r="K170" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="L170" t="inlineStr"/>
       <c r="M170" t="n">
         <v>100.37</v>
       </c>
-      <c r="N170" t="inlineStr"/>
+      <c r="N170" t="n">
+        <v>92.8</v>
+      </c>
       <c r="O170" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P170" t="n">
-        <v>-9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="171">
@@ -10408,28 +10302,30 @@
         <v>1</v>
       </c>
       <c r="G171" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>Talk Of New York</t>
+          <t>Time To Turn</t>
         </is>
       </c>
       <c r="I171" t="n">
         <v>3</v>
       </c>
       <c r="J171" t="n">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="K171" t="n">
-        <v>104</v>
-      </c>
-      <c r="L171" t="inlineStr"/>
+        <v>107</v>
+      </c>
+      <c r="L171" t="n">
+        <v>5.5</v>
+      </c>
       <c r="M171" t="n">
         <v>100.37</v>
       </c>
       <c r="N171" t="n">
-        <v>92.8</v>
+        <v>81.7</v>
       </c>
       <c r="O171" t="inlineStr">
         <is>
@@ -10466,30 +10362,30 @@
         <v>1</v>
       </c>
       <c r="G172" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>Time To Turn</t>
+          <t>Andab (IRE)</t>
         </is>
       </c>
       <c r="I172" t="n">
         <v>3</v>
       </c>
       <c r="J172" t="n">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="K172" t="n">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="L172" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="M172" t="n">
         <v>100.37</v>
       </c>
       <c r="N172" t="n">
-        <v>81.7</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="O172" t="inlineStr">
         <is>
@@ -10526,30 +10422,30 @@
         <v>1</v>
       </c>
       <c r="G173" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>Andab (IRE)</t>
+          <t>Wise Prince (IRE)</t>
         </is>
       </c>
       <c r="I173" t="n">
         <v>3</v>
       </c>
       <c r="J173" t="n">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="K173" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L173" t="n">
-        <v>5.6</v>
+        <v>8.85</v>
       </c>
       <c r="M173" t="n">
         <v>100.37</v>
       </c>
       <c r="N173" t="n">
-        <v>79.09999999999999</v>
+        <v>71.5</v>
       </c>
       <c r="O173" t="inlineStr">
         <is>
@@ -10586,11 +10482,11 @@
         <v>1</v>
       </c>
       <c r="G174" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>Wise Prince (IRE)</t>
+          <t>Nations Hope (IRE)</t>
         </is>
       </c>
       <c r="I174" t="n">
@@ -10600,16 +10496,16 @@
         <v>128</v>
       </c>
       <c r="K174" t="n">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="L174" t="n">
-        <v>8.85</v>
+        <v>9</v>
       </c>
       <c r="M174" t="n">
         <v>100.37</v>
       </c>
       <c r="N174" t="n">
-        <v>71.5</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="O174" t="inlineStr">
         <is>
@@ -10646,11 +10542,11 @@
         <v>1</v>
       </c>
       <c r="G175" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>Nations Hope (IRE)</t>
+          <t>Golden Knight (IRE)</t>
         </is>
       </c>
       <c r="I175" t="n">
@@ -10660,16 +10556,16 @@
         <v>128</v>
       </c>
       <c r="K175" t="n">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="L175" t="n">
-        <v>9</v>
+        <v>12.5</v>
       </c>
       <c r="M175" t="n">
         <v>100.37</v>
       </c>
       <c r="N175" t="n">
-        <v>70.59999999999999</v>
+        <v>59.2</v>
       </c>
       <c r="O175" t="inlineStr">
         <is>
@@ -10706,11 +10602,11 @@
         <v>1</v>
       </c>
       <c r="G176" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>Golden Knight (IRE)</t>
+          <t>Maximized</t>
         </is>
       </c>
       <c r="I176" t="n">
@@ -10720,16 +10616,16 @@
         <v>128</v>
       </c>
       <c r="K176" t="n">
-        <v>0</v>
+        <v>97</v>
       </c>
       <c r="L176" t="n">
-        <v>12.5</v>
+        <v>12.6</v>
       </c>
       <c r="M176" t="n">
         <v>100.37</v>
       </c>
       <c r="N176" t="n">
-        <v>59.2</v>
+        <v>58.8</v>
       </c>
       <c r="O176" t="inlineStr">
         <is>
@@ -10766,11 +10662,11 @@
         <v>1</v>
       </c>
       <c r="G177" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>Maximized</t>
+          <t>Yazin</t>
         </is>
       </c>
       <c r="I177" t="n">
@@ -10780,16 +10676,16 @@
         <v>128</v>
       </c>
       <c r="K177" t="n">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="L177" t="n">
-        <v>12.6</v>
+        <v>19.1</v>
       </c>
       <c r="M177" t="n">
         <v>100.37</v>
       </c>
       <c r="N177" t="n">
-        <v>58.8</v>
+        <v>44.3</v>
       </c>
       <c r="O177" t="inlineStr">
         <is>
@@ -10825,40 +10721,24 @@
       <c r="F178" t="n">
         <v>1</v>
       </c>
-      <c r="G178" t="n">
-        <v>8</v>
-      </c>
+      <c r="G178" t="inlineStr"/>
       <c r="H178" t="inlineStr">
         <is>
-          <t>Yazin</t>
-        </is>
-      </c>
-      <c r="I178" t="n">
-        <v>3</v>
-      </c>
-      <c r="J178" t="n">
-        <v>128</v>
-      </c>
-      <c r="K178" t="n">
-        <v>104</v>
-      </c>
-      <c r="L178" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="M178" t="n">
-        <v>100.37</v>
-      </c>
-      <c r="N178" t="n">
-        <v>44.3</v>
-      </c>
+          <t>Padraig Dawn (IRE)</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr"/>
+      <c r="J178" t="inlineStr"/>
+      <c r="K178" t="inlineStr"/>
+      <c r="L178" t="inlineStr"/>
+      <c r="M178" t="inlineStr"/>
+      <c r="N178" t="inlineStr"/>
       <c r="O178" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="P178" t="n">
-        <v>0</v>
-      </c>
+      <c r="P178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -12498,34 +12378,36 @@
         <v>4</v>
       </c>
       <c r="G206" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>Jakarta</t>
+          <t>Sea Suite (IRE)</t>
         </is>
       </c>
       <c r="I206" t="n">
         <v>4</v>
       </c>
       <c r="J206" t="n">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="K206" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="L206" t="inlineStr"/>
       <c r="M206" t="n">
         <v>84.53</v>
       </c>
-      <c r="N206" t="inlineStr"/>
+      <c r="N206" t="n">
+        <v>62.8</v>
+      </c>
       <c r="O206" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P206" t="n">
-        <v>-8.5</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="207">
@@ -12554,34 +12436,38 @@
         <v>4</v>
       </c>
       <c r="G207" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>Drifts Away</t>
+          <t>Zubaru</t>
         </is>
       </c>
       <c r="I207" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J207" t="n">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="K207" t="n">
-        <v>77</v>
-      </c>
-      <c r="L207" t="inlineStr"/>
+        <v>82</v>
+      </c>
+      <c r="L207" t="n">
+        <v>0.1</v>
+      </c>
       <c r="M207" t="n">
         <v>84.53</v>
       </c>
-      <c r="N207" t="inlineStr"/>
+      <c r="N207" t="n">
+        <v>72.59999999999999</v>
+      </c>
       <c r="O207" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P207" t="n">
-        <v>-8.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="208">
@@ -12610,28 +12496,30 @@
         <v>4</v>
       </c>
       <c r="G208" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>Sea Suite (IRE)</t>
+          <t>Stenmark (IRE)</t>
         </is>
       </c>
       <c r="I208" t="n">
         <v>4</v>
       </c>
       <c r="J208" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="K208" t="n">
-        <v>75</v>
-      </c>
-      <c r="L208" t="inlineStr"/>
+        <v>76</v>
+      </c>
+      <c r="L208" t="n">
+        <v>0.25</v>
+      </c>
       <c r="M208" t="n">
         <v>84.53</v>
       </c>
       <c r="N208" t="n">
-        <v>68.3</v>
+        <v>67.5</v>
       </c>
       <c r="O208" t="inlineStr">
         <is>
@@ -12639,7 +12527,7 @@
         </is>
       </c>
       <c r="P208" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="209">
@@ -12668,30 +12556,30 @@
         <v>4</v>
       </c>
       <c r="G209" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>Zubaru</t>
+          <t>Berry Clever</t>
         </is>
       </c>
       <c r="I209" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J209" t="n">
-        <v>137</v>
+        <v>125</v>
       </c>
       <c r="K209" t="n">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="L209" t="n">
-        <v>0.1</v>
+        <v>0.75</v>
       </c>
       <c r="M209" t="n">
         <v>84.53</v>
       </c>
       <c r="N209" t="n">
-        <v>72.59999999999999</v>
+        <v>59.1</v>
       </c>
       <c r="O209" t="inlineStr">
         <is>
@@ -12699,7 +12587,7 @@
         </is>
       </c>
       <c r="P209" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="210">
@@ -12728,30 +12616,30 @@
         <v>4</v>
       </c>
       <c r="G210" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>Stenmark (IRE)</t>
+          <t>Daring Legend</t>
         </is>
       </c>
       <c r="I210" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J210" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="K210" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="L210" t="n">
-        <v>0.25</v>
+        <v>2</v>
       </c>
       <c r="M210" t="n">
         <v>84.53</v>
       </c>
       <c r="N210" t="n">
-        <v>67.5</v>
+        <v>62.2</v>
       </c>
       <c r="O210" t="inlineStr">
         <is>
@@ -12759,7 +12647,7 @@
         </is>
       </c>
       <c r="P210" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="211">
@@ -12788,30 +12676,30 @@
         <v>4</v>
       </c>
       <c r="G211" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>Berry Clever</t>
+          <t>Dapper Guest (IRE)</t>
         </is>
       </c>
       <c r="I211" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J211" t="n">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="K211" t="n">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="L211" t="n">
-        <v>0.75</v>
+        <v>5.75</v>
       </c>
       <c r="M211" t="n">
         <v>84.53</v>
       </c>
       <c r="N211" t="n">
-        <v>64.09999999999999</v>
+        <v>53.5</v>
       </c>
       <c r="O211" t="inlineStr">
         <is>
@@ -12848,30 +12736,30 @@
         <v>4</v>
       </c>
       <c r="G212" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>Daring Legend</t>
+          <t>Fifty Nifty (IRE)</t>
         </is>
       </c>
       <c r="I212" t="n">
         <v>5</v>
       </c>
       <c r="J212" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="K212" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="L212" t="n">
-        <v>2</v>
+        <v>10.75</v>
       </c>
       <c r="M212" t="n">
         <v>84.53</v>
       </c>
       <c r="N212" t="n">
-        <v>62.2</v>
+        <v>38.1</v>
       </c>
       <c r="O212" t="inlineStr">
         <is>
@@ -12907,40 +12795,24 @@
       <c r="F213" t="n">
         <v>4</v>
       </c>
-      <c r="G213" t="n">
-        <v>6</v>
-      </c>
+      <c r="G213" t="inlineStr"/>
       <c r="H213" t="inlineStr">
         <is>
-          <t>Dapper Guest (IRE)</t>
-        </is>
-      </c>
-      <c r="I213" t="n">
-        <v>4</v>
-      </c>
-      <c r="J213" t="n">
-        <v>137</v>
-      </c>
-      <c r="K213" t="n">
-        <v>82</v>
-      </c>
-      <c r="L213" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="M213" t="n">
-        <v>84.53</v>
-      </c>
-      <c r="N213" t="n">
-        <v>56.5</v>
-      </c>
+          <t>Jakarta</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr"/>
+      <c r="J213" t="inlineStr"/>
+      <c r="K213" t="inlineStr"/>
+      <c r="L213" t="inlineStr"/>
+      <c r="M213" t="inlineStr"/>
+      <c r="N213" t="inlineStr"/>
       <c r="O213" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="P213" t="n">
-        <v>0</v>
-      </c>
+      <c r="P213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -12967,40 +12839,24 @@
       <c r="F214" t="n">
         <v>4</v>
       </c>
-      <c r="G214" t="n">
-        <v>7</v>
-      </c>
+      <c r="G214" t="inlineStr"/>
       <c r="H214" t="inlineStr">
         <is>
-          <t>Fifty Nifty (IRE)</t>
-        </is>
-      </c>
-      <c r="I214" t="n">
-        <v>5</v>
-      </c>
-      <c r="J214" t="n">
-        <v>133</v>
-      </c>
-      <c r="K214" t="n">
-        <v>78</v>
-      </c>
-      <c r="L214" t="n">
-        <v>10.75</v>
-      </c>
-      <c r="M214" t="n">
-        <v>84.53</v>
-      </c>
-      <c r="N214" t="n">
-        <v>38.1</v>
-      </c>
+          <t>Drifts Away</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr"/>
+      <c r="J214" t="inlineStr"/>
+      <c r="K214" t="inlineStr"/>
+      <c r="L214" t="inlineStr"/>
+      <c r="M214" t="inlineStr"/>
+      <c r="N214" t="inlineStr"/>
       <c r="O214" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="P214" t="n">
-        <v>0</v>
-      </c>
+      <c r="P214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -13318,34 +13174,36 @@
         <v>5</v>
       </c>
       <c r="G220" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>Give Me The Night (IRE)</t>
+          <t>Hengest</t>
         </is>
       </c>
       <c r="I220" t="n">
         <v>4</v>
       </c>
       <c r="J220" t="n">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="K220" t="n">
-        <v>64</v>
+        <v>78</v>
       </c>
       <c r="L220" t="inlineStr"/>
       <c r="M220" t="n">
         <v>130.21</v>
       </c>
-      <c r="N220" t="inlineStr"/>
+      <c r="N220" t="n">
+        <v>55.9</v>
+      </c>
       <c r="O220" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P220" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="221">
@@ -13374,28 +13232,30 @@
         <v>5</v>
       </c>
       <c r="G221" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>Hengest</t>
+          <t>Kings Hand</t>
         </is>
       </c>
       <c r="I221" t="n">
         <v>4</v>
       </c>
       <c r="J221" t="n">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="K221" t="n">
-        <v>78</v>
-      </c>
-      <c r="L221" t="inlineStr"/>
+        <v>74</v>
+      </c>
+      <c r="L221" t="n">
+        <v>0.75</v>
+      </c>
       <c r="M221" t="n">
         <v>130.21</v>
       </c>
       <c r="N221" t="n">
-        <v>55.9</v>
+        <v>51.2</v>
       </c>
       <c r="O221" t="inlineStr">
         <is>
@@ -13432,30 +13292,30 @@
         <v>5</v>
       </c>
       <c r="G222" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>Kings Hand</t>
+          <t>Harlington (FR)</t>
         </is>
       </c>
       <c r="I222" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J222" t="n">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="K222" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="L222" t="n">
-        <v>0.75</v>
+        <v>3.25</v>
       </c>
       <c r="M222" t="n">
         <v>130.21</v>
       </c>
       <c r="N222" t="n">
-        <v>51.2</v>
+        <v>41</v>
       </c>
       <c r="O222" t="inlineStr">
         <is>
@@ -13492,30 +13352,30 @@
         <v>5</v>
       </c>
       <c r="G223" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>Harlington (FR)</t>
+          <t>Man Of Desert</t>
         </is>
       </c>
       <c r="I223" t="n">
         <v>5</v>
       </c>
       <c r="J223" t="n">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="K223" t="n">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="L223" t="n">
-        <v>3.25</v>
+        <v>6.5</v>
       </c>
       <c r="M223" t="n">
         <v>130.21</v>
       </c>
       <c r="N223" t="n">
-        <v>44.5</v>
+        <v>36.3</v>
       </c>
       <c r="O223" t="inlineStr">
         <is>
@@ -13551,40 +13411,24 @@
       <c r="F224" t="n">
         <v>5</v>
       </c>
-      <c r="G224" t="n">
-        <v>4</v>
-      </c>
+      <c r="G224" t="inlineStr"/>
       <c r="H224" t="inlineStr">
         <is>
-          <t>Man Of Desert</t>
-        </is>
-      </c>
-      <c r="I224" t="n">
-        <v>5</v>
-      </c>
-      <c r="J224" t="n">
-        <v>132</v>
-      </c>
-      <c r="K224" t="n">
-        <v>70</v>
-      </c>
-      <c r="L224" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M224" t="n">
-        <v>130.21</v>
-      </c>
-      <c r="N224" t="n">
-        <v>36.3</v>
-      </c>
+          <t>Give Me The Night (IRE)</t>
+        </is>
+      </c>
+      <c r="I224" t="inlineStr"/>
+      <c r="J224" t="inlineStr"/>
+      <c r="K224" t="inlineStr"/>
+      <c r="L224" t="inlineStr"/>
+      <c r="M224" t="inlineStr"/>
+      <c r="N224" t="inlineStr"/>
       <c r="O224" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="P224" t="n">
-        <v>0</v>
-      </c>
+      <c r="P224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -13612,11 +13456,11 @@
         <v>4</v>
       </c>
       <c r="G225" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>Valley Ofthe Kings (SAF)</t>
+          <t>Another Abbot (IRE)</t>
         </is>
       </c>
       <c r="I225" t="n">
@@ -13632,14 +13476,16 @@
       <c r="M225" t="n">
         <v>70.04000000000001</v>
       </c>
-      <c r="N225" t="inlineStr"/>
+      <c r="N225" t="n">
+        <v>86.7</v>
+      </c>
       <c r="O225" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P225" t="n">
-        <v>-9.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="226">
@@ -13668,34 +13514,38 @@
         <v>4</v>
       </c>
       <c r="G226" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>Fantasy Master</t>
+          <t>Neyvas Angel</t>
         </is>
       </c>
       <c r="I226" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J226" t="n">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="K226" t="n">
-        <v>71</v>
-      </c>
-      <c r="L226" t="inlineStr"/>
+        <v>69</v>
+      </c>
+      <c r="L226" t="n">
+        <v>0.1</v>
+      </c>
       <c r="M226" t="n">
         <v>70.04000000000001</v>
       </c>
-      <c r="N226" t="inlineStr"/>
+      <c r="N226" t="n">
+        <v>77.59999999999999</v>
+      </c>
       <c r="O226" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P226" t="n">
-        <v>-9.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="227">
@@ -13724,28 +13574,30 @@
         <v>4</v>
       </c>
       <c r="G227" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>Another Abbot (IRE)</t>
+          <t>Carbine Harvester (FR)</t>
         </is>
       </c>
       <c r="I227" t="n">
         <v>4</v>
       </c>
       <c r="J227" t="n">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="K227" t="n">
-        <v>82</v>
-      </c>
-      <c r="L227" t="inlineStr"/>
+        <v>76</v>
+      </c>
+      <c r="L227" t="n">
+        <v>6.6</v>
+      </c>
       <c r="M227" t="n">
         <v>70.04000000000001</v>
       </c>
       <c r="N227" t="n">
-        <v>86.7</v>
+        <v>68.3</v>
       </c>
       <c r="O227" t="inlineStr">
         <is>
@@ -13782,30 +13634,30 @@
         <v>4</v>
       </c>
       <c r="G228" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>Neyvas Angel</t>
+          <t>Travel Agent (IRE)</t>
         </is>
       </c>
       <c r="I228" t="n">
         <v>4</v>
       </c>
       <c r="J228" t="n">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="K228" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="L228" t="n">
-        <v>0.1</v>
+        <v>8.6</v>
       </c>
       <c r="M228" t="n">
         <v>70.04000000000001</v>
       </c>
       <c r="N228" t="n">
-        <v>77.59999999999999</v>
+        <v>58.6</v>
       </c>
       <c r="O228" t="inlineStr">
         <is>
@@ -13813,7 +13665,7 @@
         </is>
       </c>
       <c r="P228" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="229">
@@ -13842,30 +13694,30 @@
         <v>4</v>
       </c>
       <c r="G229" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>Carbine Harvester (FR)</t>
+          <t>Twilight Fun</t>
         </is>
       </c>
       <c r="I229" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J229" t="n">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="K229" t="n">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="L229" t="n">
-        <v>6.6</v>
+        <v>8.6</v>
       </c>
       <c r="M229" t="n">
         <v>70.04000000000001</v>
       </c>
       <c r="N229" t="n">
-        <v>68.3</v>
+        <v>65.3</v>
       </c>
       <c r="O229" t="inlineStr">
         <is>
@@ -13902,30 +13754,30 @@
         <v>4</v>
       </c>
       <c r="G230" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>Twilight Fun</t>
+          <t>First Folio</t>
         </is>
       </c>
       <c r="I230" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J230" t="n">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="K230" t="n">
         <v>80</v>
       </c>
       <c r="L230" t="n">
-        <v>8.6</v>
+        <v>9.85</v>
       </c>
       <c r="M230" t="n">
         <v>70.04000000000001</v>
       </c>
       <c r="N230" t="n">
-        <v>65.3</v>
+        <v>57.1</v>
       </c>
       <c r="O230" t="inlineStr">
         <is>
@@ -13962,30 +13814,30 @@
         <v>4</v>
       </c>
       <c r="G231" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>Travel Agent (IRE)</t>
+          <t>Izzy Fast</t>
         </is>
       </c>
       <c r="I231" t="n">
         <v>4</v>
       </c>
       <c r="J231" t="n">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="K231" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="L231" t="n">
-        <v>8.6</v>
+        <v>11.6</v>
       </c>
       <c r="M231" t="n">
         <v>70.04000000000001</v>
       </c>
       <c r="N231" t="n">
-        <v>58.6</v>
+        <v>43</v>
       </c>
       <c r="O231" t="inlineStr">
         <is>
@@ -13993,7 +13845,7 @@
         </is>
       </c>
       <c r="P231" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="232">
@@ -14022,30 +13874,30 @@
         <v>4</v>
       </c>
       <c r="G232" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>First Folio</t>
+          <t>Style King (IRE)</t>
         </is>
       </c>
       <c r="I232" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J232" t="n">
-        <v>135</v>
+        <v>113</v>
       </c>
       <c r="K232" t="n">
-        <v>80</v>
+        <v>63</v>
       </c>
       <c r="L232" t="n">
-        <v>9.85</v>
+        <v>11.7</v>
       </c>
       <c r="M232" t="n">
         <v>70.04000000000001</v>
       </c>
       <c r="N232" t="n">
-        <v>60.5</v>
+        <v>34.6</v>
       </c>
       <c r="O232" t="inlineStr">
         <is>
@@ -14053,7 +13905,7 @@
         </is>
       </c>
       <c r="P232" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="233">
@@ -14081,40 +13933,24 @@
       <c r="F233" t="n">
         <v>4</v>
       </c>
-      <c r="G233" t="n">
-        <v>7</v>
-      </c>
+      <c r="G233" t="inlineStr"/>
       <c r="H233" t="inlineStr">
         <is>
-          <t>Izzy Fast</t>
-        </is>
-      </c>
-      <c r="I233" t="n">
-        <v>4</v>
-      </c>
-      <c r="J233" t="n">
-        <v>125</v>
-      </c>
-      <c r="K233" t="n">
-        <v>70</v>
-      </c>
-      <c r="L233" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="M233" t="n">
-        <v>70.04000000000001</v>
-      </c>
-      <c r="N233" t="n">
-        <v>43</v>
-      </c>
+          <t>Valley Ofthe Kings (SAF)</t>
+        </is>
+      </c>
+      <c r="I233" t="inlineStr"/>
+      <c r="J233" t="inlineStr"/>
+      <c r="K233" t="inlineStr"/>
+      <c r="L233" t="inlineStr"/>
+      <c r="M233" t="inlineStr"/>
+      <c r="N233" t="inlineStr"/>
       <c r="O233" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="P233" t="n">
-        <v>0</v>
-      </c>
+      <c r="P233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -14141,40 +13977,24 @@
       <c r="F234" t="n">
         <v>4</v>
       </c>
-      <c r="G234" t="n">
-        <v>8</v>
-      </c>
+      <c r="G234" t="inlineStr"/>
       <c r="H234" t="inlineStr">
         <is>
-          <t>Style King (IRE)</t>
-        </is>
-      </c>
-      <c r="I234" t="n">
-        <v>4</v>
-      </c>
-      <c r="J234" t="n">
-        <v>118</v>
-      </c>
-      <c r="K234" t="n">
-        <v>63</v>
-      </c>
-      <c r="L234" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="M234" t="n">
-        <v>70.04000000000001</v>
-      </c>
-      <c r="N234" t="n">
-        <v>37.8</v>
-      </c>
+          <t>Fantasy Master</t>
+        </is>
+      </c>
+      <c r="I234" t="inlineStr"/>
+      <c r="J234" t="inlineStr"/>
+      <c r="K234" t="inlineStr"/>
+      <c r="L234" t="inlineStr"/>
+      <c r="M234" t="inlineStr"/>
+      <c r="N234" t="inlineStr"/>
       <c r="O234" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="P234" t="n">
-        <v>0</v>
-      </c>
+      <c r="P234" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -14571,7 +14391,7 @@
         <v>4</v>
       </c>
       <c r="J241" t="n">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="K241" t="n">
         <v>57</v>
@@ -14583,7 +14403,7 @@
         <v>98.23</v>
       </c>
       <c r="N241" t="n">
-        <v>25.5</v>
+        <v>23</v>
       </c>
       <c r="O241" t="inlineStr">
         <is>
